--- a/data/trans_bre/P16A_n_R3-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,42</t>
+          <t>-1,5; 2,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,84</t>
+          <t>-0,67; 3,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,78</t>
+          <t>-1,66; 1,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,07</t>
+          <t>-0,03; 4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 321,55</t>
+          <t>-75,17; 330,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,5; —</t>
+          <t>-59,0; inf</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-80,74; 265,67</t>
+          <t>-75,72; 263,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 210,11</t>
+          <t>-2,88; 235,53</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,87</t>
+          <t>-1,28; 1,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,46</t>
+          <t>-2,03; 2,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,02</t>
+          <t>0,11; 3,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,17</t>
+          <t>-1,66; 3,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 283,84</t>
+          <t>-69,24; 291,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 94,06</t>
+          <t>-30,16; 97,75</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,04</t>
+          <t>-0,74; 4,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,51</t>
+          <t>-1,97; 3,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 10,12</t>
+          <t>1,32; 9,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 14,27</t>
+          <t>4,28; 14,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 610,73</t>
+          <t>-59,84; 523,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,65; 186,77</t>
+          <t>-54,73; 202,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,7; 1712,53</t>
+          <t>60,14; 1600,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,68; 808,56</t>
+          <t>60,98; 819,63</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,87</t>
+          <t>-0,66; 1,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,54</t>
+          <t>0,32; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,79</t>
+          <t>-0,3; 2,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,07</t>
+          <t>-3,99; 0,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 142,98</t>
+          <t>-32,52; 146,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 308,42</t>
+          <t>10,93; 265,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 206,76</t>
+          <t>-15,78; 185,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 19,74</t>
+          <t>-57,86; 17,54</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,59</t>
+          <t>-2,36; 1,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,37</t>
+          <t>2,29; 6,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,75</t>
+          <t>0,37; 4,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,39</t>
+          <t>4,43; 11,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 148,05</t>
+          <t>-68,71; 108,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,25; 611,68</t>
+          <t>65,68; 632,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 226,49</t>
+          <t>6,22; 220,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,28; 249,74</t>
+          <t>61,75; 246,14</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,98</t>
+          <t>2,73; 4,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,84</t>
+          <t>5,58; 8,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,21</t>
+          <t>3,63; 7,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,9; 13,55</t>
+          <t>8,83; 13,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>278,68; 2554,92</t>
+          <t>288,23; 2119,59</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,76</t>
+          <t>0,34; 1,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,14</t>
+          <t>2,24; 4,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,52</t>
+          <t>1,87; 3,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,01</t>
+          <t>3,0; 6,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,27; 150,45</t>
+          <t>17,62; 140,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>103,09; 288,85</t>
+          <t>100,1; 277,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,03; 256,22</t>
+          <t>92,13; 261,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>58,16; 159,0</t>
+          <t>61,76; 163,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R3-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,37</t>
+          <t>-1,43; 2,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,73</t>
+          <t>-0,73; 3,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,72</t>
+          <t>-1,97; 1,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,18</t>
+          <t>0,08; 4,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 330,8</t>
+          <t>-72,63; 345,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,0; inf</t>
+          <t>-67,39; 1199,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-75,72; 263,33</t>
+          <t>-77,9; 305,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 235,53</t>
+          <t>-1,03; 208,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,01</t>
+          <t>-1,27; 0,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,57</t>
+          <t>-2,27; 2,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,17</t>
+          <t>0,11; 2,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,22</t>
+          <t>-1,58; 3,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 291,95</t>
+          <t>-71,33; 307,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 97,75</t>
+          <t>-27,43; 99,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,42</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>200,99%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,66</t>
+          <t>-0,82; 4,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,66</t>
+          <t>-2,05; 3,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,35</t>
+          <t>1,28; 9,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,73</t>
+          <t>1,75; 10,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,84; 523,88</t>
+          <t>-50,86; 580,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 202,51</t>
+          <t>-56,13; 183,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,14; 1600,22</t>
+          <t>37,41; 1577,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60,98; 819,63</t>
+          <t>21,75; 188,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,99</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,15%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,9</t>
+          <t>-0,74; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,32</t>
+          <t>0,39; 3,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,68</t>
+          <t>-0,07; 2,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,96</t>
+          <t>-1,53; 1,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 146,15</t>
+          <t>-34,45; 138,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,93; 265,65</t>
+          <t>15,72; 297,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 185,95</t>
+          <t>-4,52; 204,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 17,54</t>
+          <t>-23,14; 40,07</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>9,87</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>145,33%</t>
+          <t>195,82%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,41</t>
+          <t>-2,38; 1,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,39</t>
+          <t>2,18; 6,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,89</t>
+          <t>0,49; 4,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,72</t>
+          <t>7,32; 12,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,71; 108,91</t>
+          <t>-70,88; 115,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,68; 632,7</t>
+          <t>67,53; 621,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 220,02</t>
+          <t>11,03; 222,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,75; 246,14</t>
+          <t>114,05; 325,07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,26</t>
+          <t>11,08</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>743,58%</t>
+          <t>723,27%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,85</t>
+          <t>2,67; 4,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,76</t>
+          <t>5,67; 8,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,09</t>
+          <t>3,76; 7,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,4</t>
+          <t>8,72; 13,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>288,23; 2119,59</t>
+          <t>251,85; 2026,71</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>100,59%</t>
+          <t>104,09%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,79</t>
+          <t>0,35; 1,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,11</t>
+          <t>2,22; 4,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,54</t>
+          <t>1,83; 3,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,04</t>
+          <t>3,94; 5,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 140,5</t>
+          <t>19,15; 148,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>100,1; 277,57</t>
+          <t>93,31; 270,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,13; 261,45</t>
+          <t>92,12; 257,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61,76; 163,8</t>
+          <t>75,4; 140,45</t>
         </is>
       </c>
     </row>
